--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260828.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260828.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>439,785,600</t>
+          <t>23,537,580</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>23,537,580</t>
+          <t>439,785,600</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>38,542,991</t>
+          <t>22,513,197</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>22,513,197</t>
+          <t>38,542,991</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>32,559,693</t>
+          <t>10,959,255</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>10,959,255</t>
+          <t>32,559,693</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
